--- a/artfynd/A 58400-2021 artfynd.xlsx
+++ b/artfynd/A 58400-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58400-2021 artfynd.xlsx
+++ b/artfynd/A 58400-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107469675</v>
+        <v>107469682</v>
       </c>
       <c r="B2" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3215</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453159.7758487229</v>
+        <v>453160</v>
       </c>
       <c r="R2" t="n">
-        <v>6562668.966957627</v>
+        <v>6562669</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>2015-10-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-10-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107469681</v>
+        <v>107469675</v>
       </c>
       <c r="B3" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453159.7758487229</v>
+        <v>453160</v>
       </c>
       <c r="R3" t="n">
-        <v>6562668.966957627</v>
+        <v>6562669</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -864,21 +844,11 @@
           <t>2015-10-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-10-16</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -887,11 +857,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Gammal gran (GAMGRAN)</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -912,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107469676</v>
+        <v>107469681</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453159.7758487229</v>
+        <v>453160</v>
       </c>
       <c r="R4" t="n">
-        <v>6562668.966957627</v>
+        <v>6562669</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -985,21 +945,11 @@
           <t>2015-10-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2015-10-16</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1011,7 +961,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Gammal tall (GAMTALL)</t>
+          <t>Gammal gran (GAMGRAN)</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1033,15 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107469682</v>
+        <v>107469679</v>
       </c>
       <c r="B5" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1049,21 +994,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1073,10 +1018,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>453159.7758487229</v>
+        <v>453160</v>
       </c>
       <c r="R5" t="n">
-        <v>6562668.966957627</v>
+        <v>6562669</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1106,21 +1051,11 @@
           <t>2015-10-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2015-10-16</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1129,6 +1064,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Gammal gran (GAMGRAN)</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1149,15 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>107469679</v>
+        <v>107469676</v>
       </c>
       <c r="B6" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,16 +1100,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1189,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>453159.7758487229</v>
+        <v>453160</v>
       </c>
       <c r="R6" t="n">
-        <v>6562668.966957627</v>
+        <v>6562669</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -1222,21 +1157,11 @@
           <t>2015-10-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2015-10-16</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1248,7 +1173,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Gammal gran (GAMGRAN)</t>
+          <t>Gammal tall (GAMTALL)</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 58400-2021 artfynd.xlsx
+++ b/artfynd/A 58400-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107469682</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107469675</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107469681</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107469679</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,8 +1217,20 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107469676</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>